--- a/R/scenarios_bin_nonstratified_fixed.xlsx
+++ b/R/scenarios_bin_nonstratified_fixed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Research\01 Tom PC blocked randomisation\design effects\partclus_blockedrand\R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Research\01 Tom PC blocked randomisation\design effects\clean files for public repo\R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44D88C3-2204-4F27-A3B4-F82DA24CD216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426E8D92-30E6-438D-A03C-697C21D896C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="23120" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12560" yWindow="1780" windowWidth="23760" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios" sheetId="1" r:id="rId1"/>
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>0.2</v>
@@ -882,10 +882,10 @@
         <v>0.4</v>
       </c>
       <c r="F22">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="G22">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>0.8</v>
@@ -905,10 +905,10 @@
         <v>0.4</v>
       </c>
       <c r="F23">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="G23">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -916,7 +916,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>0.2</v>
@@ -928,10 +928,10 @@
         <v>0.4</v>
       </c>
       <c r="F24">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="G24">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -939,7 +939,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>0.8</v>
@@ -951,10 +951,10 @@
         <v>0.4</v>
       </c>
       <c r="F25">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="G25">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -962,7 +962,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>0.2</v>
@@ -974,10 +974,10 @@
         <v>0.4</v>
       </c>
       <c r="F26">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="G26">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -985,7 +985,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>0.8</v>
@@ -997,10 +997,10 @@
         <v>0.4</v>
       </c>
       <c r="F27">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="G27">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -1008,7 +1008,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>0.2</v>
@@ -1020,10 +1020,10 @@
         <v>0.4</v>
       </c>
       <c r="F28">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="G28">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -1031,7 +1031,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C29">
         <v>0.8</v>
@@ -1043,10 +1043,10 @@
         <v>0.4</v>
       </c>
       <c r="F29">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="G29">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1054,7 +1054,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>0.2</v>
@@ -1077,7 +1077,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>0.8</v>
@@ -1100,7 +1100,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>0.2</v>
@@ -1123,7 +1123,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>0.8</v>
@@ -1146,7 +1146,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C34">
         <v>0.2</v>
@@ -1169,7 +1169,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>0.8</v>
@@ -1192,7 +1192,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C36">
         <v>0.2</v>
@@ -1215,7 +1215,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C37">
         <v>0.8</v>
@@ -1238,7 +1238,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C38">
         <v>0.2</v>
@@ -1261,7 +1261,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C39">
         <v>0.8</v>
@@ -1284,7 +1284,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C40">
         <v>0.2</v>
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C41">
         <v>0.8</v>
@@ -1322,374 +1322,6 @@
         <v>256</v>
       </c>
       <c r="G41">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42">
-        <v>8</v>
-      </c>
-      <c r="C42">
-        <v>0.2</v>
-      </c>
-      <c r="D42">
-        <v>0.3</v>
-      </c>
-      <c r="E42">
-        <v>0.4</v>
-      </c>
-      <c r="F42">
-        <v>128</v>
-      </c>
-      <c r="G42">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43">
-        <v>8</v>
-      </c>
-      <c r="C43">
-        <v>0.8</v>
-      </c>
-      <c r="D43">
-        <v>0.3</v>
-      </c>
-      <c r="E43">
-        <v>0.4</v>
-      </c>
-      <c r="F43">
-        <v>128</v>
-      </c>
-      <c r="G43">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44">
-        <v>8</v>
-      </c>
-      <c r="C44">
-        <v>0.2</v>
-      </c>
-      <c r="D44">
-        <v>0.3</v>
-      </c>
-      <c r="E44">
-        <v>0.4</v>
-      </c>
-      <c r="F44">
-        <v>256</v>
-      </c>
-      <c r="G44">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45">
-        <v>8</v>
-      </c>
-      <c r="C45">
-        <v>0.8</v>
-      </c>
-      <c r="D45">
-        <v>0.3</v>
-      </c>
-      <c r="E45">
-        <v>0.4</v>
-      </c>
-      <c r="F45">
-        <v>256</v>
-      </c>
-      <c r="G45">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46">
-        <v>10</v>
-      </c>
-      <c r="C46">
-        <v>0.2</v>
-      </c>
-      <c r="D46">
-        <v>0.3</v>
-      </c>
-      <c r="E46">
-        <v>0.4</v>
-      </c>
-      <c r="F46">
-        <v>128</v>
-      </c>
-      <c r="G46">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47">
-        <v>10</v>
-      </c>
-      <c r="C47">
-        <v>0.8</v>
-      </c>
-      <c r="D47">
-        <v>0.3</v>
-      </c>
-      <c r="E47">
-        <v>0.4</v>
-      </c>
-      <c r="F47">
-        <v>128</v>
-      </c>
-      <c r="G47">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48">
-        <v>10</v>
-      </c>
-      <c r="C48">
-        <v>0.2</v>
-      </c>
-      <c r="D48">
-        <v>0.3</v>
-      </c>
-      <c r="E48">
-        <v>0.4</v>
-      </c>
-      <c r="F48">
-        <v>256</v>
-      </c>
-      <c r="G48">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49">
-        <v>10</v>
-      </c>
-      <c r="C49">
-        <v>0.8</v>
-      </c>
-      <c r="D49">
-        <v>0.3</v>
-      </c>
-      <c r="E49">
-        <v>0.4</v>
-      </c>
-      <c r="F49">
-        <v>256</v>
-      </c>
-      <c r="G49">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50">
-        <v>12</v>
-      </c>
-      <c r="C50">
-        <v>0.2</v>
-      </c>
-      <c r="D50">
-        <v>0.3</v>
-      </c>
-      <c r="E50">
-        <v>0.4</v>
-      </c>
-      <c r="F50">
-        <v>128</v>
-      </c>
-      <c r="G50">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51">
-        <v>12</v>
-      </c>
-      <c r="C51">
-        <v>0.8</v>
-      </c>
-      <c r="D51">
-        <v>0.3</v>
-      </c>
-      <c r="E51">
-        <v>0.4</v>
-      </c>
-      <c r="F51">
-        <v>128</v>
-      </c>
-      <c r="G51">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52">
-        <v>12</v>
-      </c>
-      <c r="C52">
-        <v>0.2</v>
-      </c>
-      <c r="D52">
-        <v>0.3</v>
-      </c>
-      <c r="E52">
-        <v>0.4</v>
-      </c>
-      <c r="F52">
-        <v>256</v>
-      </c>
-      <c r="G52">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53">
-        <v>12</v>
-      </c>
-      <c r="C53">
-        <v>0.8</v>
-      </c>
-      <c r="D53">
-        <v>0.3</v>
-      </c>
-      <c r="E53">
-        <v>0.4</v>
-      </c>
-      <c r="F53">
-        <v>256</v>
-      </c>
-      <c r="G53">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54">
-        <v>14</v>
-      </c>
-      <c r="C54">
-        <v>0.2</v>
-      </c>
-      <c r="D54">
-        <v>0.3</v>
-      </c>
-      <c r="E54">
-        <v>0.4</v>
-      </c>
-      <c r="F54">
-        <v>128</v>
-      </c>
-      <c r="G54">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55">
-        <v>14</v>
-      </c>
-      <c r="C55">
-        <v>0.8</v>
-      </c>
-      <c r="D55">
-        <v>0.3</v>
-      </c>
-      <c r="E55">
-        <v>0.4</v>
-      </c>
-      <c r="F55">
-        <v>128</v>
-      </c>
-      <c r="G55">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56">
-        <v>14</v>
-      </c>
-      <c r="C56">
-        <v>0.2</v>
-      </c>
-      <c r="D56">
-        <v>0.3</v>
-      </c>
-      <c r="E56">
-        <v>0.4</v>
-      </c>
-      <c r="F56">
-        <v>256</v>
-      </c>
-      <c r="G56">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57">
-        <v>14</v>
-      </c>
-      <c r="C57">
-        <v>0.8</v>
-      </c>
-      <c r="D57">
-        <v>0.3</v>
-      </c>
-      <c r="E57">
-        <v>0.4</v>
-      </c>
-      <c r="F57">
-        <v>256</v>
-      </c>
-      <c r="G57">
         <v>256</v>
       </c>
     </row>
